--- a/Robotica_LAB/LAB_2/Lab_2.xlsx
+++ b/Robotica_LAB/LAB_2/Lab_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Semestre\Cursando\Robotica_LAB\LAB_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AC5AFA6-DB7C-46C2-94DB-AF66E12DBC66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{954E9B30-6CE5-4550-A596-FD111BB15864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="104">
   <si>
     <t>Ubicacion</t>
   </si>
@@ -291,7 +291,52 @@
     <t>CN11 - 63</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>ADC1</t>
+  </si>
+  <si>
+    <t>IN4</t>
+  </si>
+  <si>
+    <t>PA4</t>
+  </si>
+  <si>
+    <t>CN7 - 17</t>
+  </si>
+  <si>
+    <t>IN5</t>
+  </si>
+  <si>
+    <t>PA5</t>
+  </si>
+  <si>
+    <t>CN7 - 10</t>
+  </si>
+  <si>
+    <t>IN10</t>
+  </si>
+  <si>
+    <t>PC0</t>
+  </si>
+  <si>
+    <t>CN9 - 3</t>
+  </si>
+  <si>
+    <t>IN11</t>
+  </si>
+  <si>
+    <t>PC1</t>
+  </si>
+  <si>
+    <t>CN11 - 36</t>
+  </si>
+  <si>
+    <t>IN12</t>
+  </si>
+  <si>
+    <t>PC2</t>
+  </si>
+  <si>
+    <t>CN10 - 9</t>
   </si>
 </sst>
 </file>
@@ -400,6 +445,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -407,9 +455,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -745,7 +790,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="H2:S25"/>
+  <dimension ref="H2:S27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="16" max="16" width="14.28515625" customWidth="1"/>
@@ -933,13 +978,13 @@
       </c>
     </row>
     <row r="11" spans="8:19" x14ac:dyDescent="0.25">
-      <c r="H11" s="7">
-        <v>1</v>
-      </c>
-      <c r="I11" s="7">
+      <c r="H11" s="4">
+        <v>1</v>
+      </c>
+      <c r="I11" s="4">
         <v>200</v>
       </c>
-      <c r="J11" s="7">
+      <c r="J11" s="4">
         <v>2</v>
       </c>
       <c r="K11" s="2">
@@ -948,7 +993,7 @@
       <c r="L11" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="M11" s="4" t="s">
+      <c r="M11" s="5" t="s">
         <v>38</v>
       </c>
       <c r="N11" s="2" t="s">
@@ -968,16 +1013,16 @@
       </c>
     </row>
     <row r="12" spans="8:19" x14ac:dyDescent="0.25">
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
       <c r="K12" s="2">
         <v>2</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M12" s="5"/>
+      <c r="M12" s="6"/>
       <c r="N12" s="2" t="s">
         <v>44</v>
       </c>
@@ -995,13 +1040,13 @@
       </c>
     </row>
     <row r="13" spans="8:19" x14ac:dyDescent="0.25">
-      <c r="H13" s="7">
+      <c r="H13" s="4">
         <v>2</v>
       </c>
-      <c r="I13" s="7">
+      <c r="I13" s="4">
         <v>80</v>
       </c>
-      <c r="J13" s="7">
+      <c r="J13" s="4">
         <v>1</v>
       </c>
       <c r="K13" s="2">
@@ -1010,7 +1055,7 @@
       <c r="L13" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="M13" s="5"/>
+      <c r="M13" s="6"/>
       <c r="N13" s="2" t="s">
         <v>24</v>
       </c>
@@ -1028,16 +1073,16 @@
       </c>
     </row>
     <row r="14" spans="8:19" x14ac:dyDescent="0.25">
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
       <c r="K14" s="2">
         <v>2</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="M14" s="5"/>
+      <c r="M14" s="6"/>
       <c r="N14" s="2" t="s">
         <v>25</v>
       </c>
@@ -1055,20 +1100,20 @@
       </c>
     </row>
     <row r="15" spans="8:19" x14ac:dyDescent="0.25">
-      <c r="H15" s="7">
+      <c r="H15" s="4">
         <v>3</v>
       </c>
-      <c r="I15" s="7">
+      <c r="I15" s="4">
         <v>80</v>
       </c>
-      <c r="J15" s="7">
+      <c r="J15" s="4">
         <v>3</v>
       </c>
       <c r="K15" s="2">
         <v>1</v>
       </c>
       <c r="L15" s="2"/>
-      <c r="M15" s="5"/>
+      <c r="M15" s="6"/>
       <c r="N15" s="2" t="s">
         <v>45</v>
       </c>
@@ -1086,14 +1131,14 @@
       </c>
     </row>
     <row r="16" spans="8:19" x14ac:dyDescent="0.25">
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
       <c r="K16" s="2">
         <v>2</v>
       </c>
       <c r="L16" s="2"/>
-      <c r="M16" s="5"/>
+      <c r="M16" s="6"/>
       <c r="N16" s="2" t="s">
         <v>46</v>
       </c>
@@ -1111,13 +1156,13 @@
       </c>
     </row>
     <row r="17" spans="8:19" x14ac:dyDescent="0.25">
-      <c r="H17" s="7">
+      <c r="H17" s="4">
         <v>4</v>
       </c>
-      <c r="I17" s="7">
+      <c r="I17" s="4">
         <v>80</v>
       </c>
-      <c r="J17" s="7">
+      <c r="J17" s="4">
         <v>4</v>
       </c>
       <c r="K17" s="2">
@@ -1126,7 +1171,7 @@
       <c r="L17" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="M17" s="5"/>
+      <c r="M17" s="6"/>
       <c r="N17" s="2" t="s">
         <v>2</v>
       </c>
@@ -1144,16 +1189,16 @@
       </c>
     </row>
     <row r="18" spans="8:19" x14ac:dyDescent="0.25">
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
       <c r="K18" s="2">
         <v>2</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="M18" s="5"/>
+      <c r="M18" s="6"/>
       <c r="N18" s="2" t="s">
         <v>26</v>
       </c>
@@ -1171,13 +1216,13 @@
       </c>
     </row>
     <row r="19" spans="8:19" x14ac:dyDescent="0.25">
-      <c r="H19" s="7">
+      <c r="H19" s="4">
         <v>5</v>
       </c>
-      <c r="I19" s="7">
+      <c r="I19" s="4">
         <v>80</v>
       </c>
-      <c r="J19" s="7">
+      <c r="J19" s="4">
         <v>8</v>
       </c>
       <c r="K19" s="2">
@@ -1186,7 +1231,7 @@
       <c r="L19" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="M19" s="5"/>
+      <c r="M19" s="6"/>
       <c r="N19" s="2" t="s">
         <v>27</v>
       </c>
@@ -1204,16 +1249,16 @@
       </c>
     </row>
     <row r="20" spans="8:19" x14ac:dyDescent="0.25">
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
       <c r="K20" s="2">
         <v>2</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="M20" s="6"/>
+      <c r="M20" s="7"/>
       <c r="N20" s="2" t="s">
         <v>28</v>
       </c>
@@ -1237,6 +1282,18 @@
       <c r="I22" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="K22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="23" spans="8:19" x14ac:dyDescent="0.25">
       <c r="H23" s="2" t="s">
@@ -1245,6 +1302,18 @@
       <c r="I23" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="K23" s="2">
+        <v>1</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="24" spans="8:19" x14ac:dyDescent="0.25">
       <c r="H24" s="2" t="s">
@@ -1253,30 +1322,79 @@
       <c r="I24" s="2" t="s">
         <v>55</v>
       </c>
+      <c r="K24" s="2">
+        <v>2</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="25" spans="8:19" x14ac:dyDescent="0.25">
-      <c r="N25" t="s">
-        <v>88</v>
+      <c r="K25" s="2">
+        <v>3</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="26" spans="8:19" x14ac:dyDescent="0.25">
+      <c r="K26" s="2">
+        <v>4</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="8:19" x14ac:dyDescent="0.25">
+      <c r="K27" s="2">
+        <v>5</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="H19:H20"/>
     <mergeCell ref="M11:M20"/>
     <mergeCell ref="J19:J20"/>
     <mergeCell ref="J17:J18"/>
     <mergeCell ref="J15:J16"/>
     <mergeCell ref="J13:J14"/>
     <mergeCell ref="J11:J12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="I19:I20"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Robotica_LAB/LAB_2/Lab_2.xlsx
+++ b/Robotica_LAB/LAB_2/Lab_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Semestre\Cursando\Robotica_LAB\LAB_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{954E9B30-6CE5-4550-A596-FD111BB15864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64BFB723-4D86-49B8-B379-BEFC69A9936A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-3345" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -445,9 +445,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -455,6 +452,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -978,13 +978,13 @@
       </c>
     </row>
     <row r="11" spans="8:19" x14ac:dyDescent="0.25">
-      <c r="H11" s="4">
-        <v>1</v>
-      </c>
-      <c r="I11" s="4">
+      <c r="H11" s="7">
+        <v>1</v>
+      </c>
+      <c r="I11" s="7">
         <v>200</v>
       </c>
-      <c r="J11" s="4">
+      <c r="J11" s="7">
         <v>2</v>
       </c>
       <c r="K11" s="2">
@@ -993,7 +993,7 @@
       <c r="L11" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="M11" s="5" t="s">
+      <c r="M11" s="4" t="s">
         <v>38</v>
       </c>
       <c r="N11" s="2" t="s">
@@ -1013,16 +1013,16 @@
       </c>
     </row>
     <row r="12" spans="8:19" x14ac:dyDescent="0.25">
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
       <c r="K12" s="2">
         <v>2</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M12" s="6"/>
+      <c r="M12" s="5"/>
       <c r="N12" s="2" t="s">
         <v>44</v>
       </c>
@@ -1040,13 +1040,13 @@
       </c>
     </row>
     <row r="13" spans="8:19" x14ac:dyDescent="0.25">
-      <c r="H13" s="4">
+      <c r="H13" s="7">
         <v>2</v>
       </c>
-      <c r="I13" s="4">
+      <c r="I13" s="7">
         <v>80</v>
       </c>
-      <c r="J13" s="4">
+      <c r="J13" s="7">
         <v>1</v>
       </c>
       <c r="K13" s="2">
@@ -1055,7 +1055,7 @@
       <c r="L13" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="M13" s="6"/>
+      <c r="M13" s="5"/>
       <c r="N13" s="2" t="s">
         <v>24</v>
       </c>
@@ -1073,16 +1073,16 @@
       </c>
     </row>
     <row r="14" spans="8:19" x14ac:dyDescent="0.25">
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
       <c r="K14" s="2">
         <v>2</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="M14" s="6"/>
+      <c r="M14" s="5"/>
       <c r="N14" s="2" t="s">
         <v>25</v>
       </c>
@@ -1100,20 +1100,20 @@
       </c>
     </row>
     <row r="15" spans="8:19" x14ac:dyDescent="0.25">
-      <c r="H15" s="4">
+      <c r="H15" s="7">
         <v>3</v>
       </c>
-      <c r="I15" s="4">
+      <c r="I15" s="7">
         <v>80</v>
       </c>
-      <c r="J15" s="4">
+      <c r="J15" s="7">
         <v>3</v>
       </c>
       <c r="K15" s="2">
         <v>1</v>
       </c>
       <c r="L15" s="2"/>
-      <c r="M15" s="6"/>
+      <c r="M15" s="5"/>
       <c r="N15" s="2" t="s">
         <v>45</v>
       </c>
@@ -1131,14 +1131,14 @@
       </c>
     </row>
     <row r="16" spans="8:19" x14ac:dyDescent="0.25">
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
       <c r="K16" s="2">
         <v>2</v>
       </c>
       <c r="L16" s="2"/>
-      <c r="M16" s="6"/>
+      <c r="M16" s="5"/>
       <c r="N16" s="2" t="s">
         <v>46</v>
       </c>
@@ -1156,13 +1156,13 @@
       </c>
     </row>
     <row r="17" spans="8:19" x14ac:dyDescent="0.25">
-      <c r="H17" s="4">
+      <c r="H17" s="7">
         <v>4</v>
       </c>
-      <c r="I17" s="4">
+      <c r="I17" s="7">
         <v>80</v>
       </c>
-      <c r="J17" s="4">
+      <c r="J17" s="7">
         <v>4</v>
       </c>
       <c r="K17" s="2">
@@ -1171,7 +1171,7 @@
       <c r="L17" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="M17" s="6"/>
+      <c r="M17" s="5"/>
       <c r="N17" s="2" t="s">
         <v>2</v>
       </c>
@@ -1189,16 +1189,16 @@
       </c>
     </row>
     <row r="18" spans="8:19" x14ac:dyDescent="0.25">
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
       <c r="K18" s="2">
         <v>2</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="M18" s="6"/>
+      <c r="M18" s="5"/>
       <c r="N18" s="2" t="s">
         <v>26</v>
       </c>
@@ -1216,13 +1216,13 @@
       </c>
     </row>
     <row r="19" spans="8:19" x14ac:dyDescent="0.25">
-      <c r="H19" s="4">
+      <c r="H19" s="7">
         <v>5</v>
       </c>
-      <c r="I19" s="4">
+      <c r="I19" s="7">
         <v>80</v>
       </c>
-      <c r="J19" s="4">
+      <c r="J19" s="7">
         <v>8</v>
       </c>
       <c r="K19" s="2">
@@ -1231,7 +1231,7 @@
       <c r="L19" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="M19" s="6"/>
+      <c r="M19" s="5"/>
       <c r="N19" s="2" t="s">
         <v>27</v>
       </c>
@@ -1249,16 +1249,16 @@
       </c>
     </row>
     <row r="20" spans="8:19" x14ac:dyDescent="0.25">
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
       <c r="K20" s="2">
         <v>2</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="M20" s="7"/>
+      <c r="M20" s="6"/>
       <c r="N20" s="2" t="s">
         <v>28</v>
       </c>
@@ -1379,22 +1379,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="H19:H20"/>
     <mergeCell ref="M11:M20"/>
     <mergeCell ref="J19:J20"/>
     <mergeCell ref="J17:J18"/>
     <mergeCell ref="J15:J16"/>
     <mergeCell ref="J13:J14"/>
     <mergeCell ref="J11:J12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="I19:I20"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
